--- a/JobIntel/sql/query_results/experience_level_distribution.xlsx
+++ b/JobIntel/sql/query_results/experience_level_distribution.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\khush\OneDrive\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/42a4dbeb8f84b5af/Desktop/AI-Powered-Job-Market-Intelligence-Platform/AI-Powered-Job-Market-Intelligence-Platform/JobIntel/sql/query_results/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{428245D9-ED26-4C78-930D-69038B2C1E3E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="6" documentId="8_{428245D9-ED26-4C78-930D-69038B2C1E3E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0E5A5B86-934D-4563-8E44-3E5D4270E17F}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{CE94D5D6-731B-4AD5-89C6-CBBF81026C38}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="7">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="10">
   <si>
     <t>Mid-Senior level</t>
   </si>
@@ -55,6 +55,15 @@
   </si>
   <si>
     <t>Executive</t>
+  </si>
+  <si>
+    <t>experience_level</t>
+  </si>
+  <si>
+    <t>job_count</t>
+  </si>
+  <si>
+    <t>pct</t>
   </si>
 </sst>
 </file>
@@ -406,83 +415,94 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C9D9178E-FF9B-4B6C-92F1-976CF339B36C}">
-  <dimension ref="A1:C7"/>
+  <dimension ref="A1:C8"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1">
-        <v>41489</v>
-      </c>
-      <c r="C1">
-        <v>33.5</v>
+        <v>7</v>
+      </c>
+      <c r="B1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C1" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B2">
-        <v>36708</v>
+        <v>41489</v>
       </c>
       <c r="C2">
-        <v>29.6</v>
+        <v>33.5</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B3">
-        <v>29409</v>
+        <v>36708</v>
       </c>
       <c r="C3">
-        <v>23.7</v>
+        <v>29.6</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B4">
-        <v>9826</v>
+        <v>29409</v>
       </c>
       <c r="C4">
-        <v>7.9</v>
+        <v>23.7</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B5">
-        <v>3746</v>
+        <v>9826</v>
       </c>
       <c r="C5">
-        <v>3</v>
+        <v>7.9</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B6">
-        <v>1449</v>
+        <v>3746</v>
       </c>
       <c r="C6">
-        <v>1.2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
+        <v>5</v>
+      </c>
+      <c r="B7">
+        <v>1449</v>
+      </c>
+      <c r="C7">
+        <v>1.2</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
         <v>6</v>
       </c>
-      <c r="B7">
+      <c r="B8">
         <v>1222</v>
       </c>
-      <c r="C7">
+      <c r="C8">
         <v>1</v>
       </c>
     </row>
